--- a/docs/db/Table_List_Schema.xlsx
+++ b/docs/db/Table_List_Schema.xlsx
@@ -4,7 +4,6 @@
   <sheets>
     <sheet name="Table List" sheetId="1" r:id="rId1"/>
     <sheet name="Table Schema" sheetId="2" r:id="rId2"/>
-    <sheet name="待DBA回覆" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -1073,7 +1072,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">目的：站台名稱、上傳限制、流程政策、存取紀錄排除 IP 等可調參數。來源：本檔預載＋後台維護。主鍵：NAME＋VALUE。多值參數（如 EXCLUDE_IP）一值一列；ADMIN_EMAIL 由部署時填入，不預載</t>
+          <t xml:space="preserve">目的：站台名稱、上傳限制、流程政策、存取紀錄排除 IP 等可調參數。來源：本檔預載＋後台維護。主鍵：PARAM_NAME＋PARAM_VALUE。多值參數（如 EXCLUDE_IP）一值一列；ADMIN_EMAIL 由部署時填入，不預載。欄名依規範 11 加 PARAM_ 前綴，與規範範例工作表的 NAME／VALUE／DESCR／MEMO 不同</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13637,7 +13636,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAME</t>
+          <t xml:space="preserve">PARAM_NAME</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -13676,7 +13675,7 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE</t>
+          <t xml:space="preserve">PARAM_VALUE</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -13715,7 +13714,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESCR</t>
+          <t xml:space="preserve">PARAM_DESC</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -13750,7 +13749,7 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEMO</t>
+          <t xml:space="preserve">PARAM_MEMO</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -15316,99 +15315,4 @@
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">問題</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本檔做法</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">請 DBA 回覆</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS_PARAM 的 NAME／VALUE／DESCR／MEMO 是單字欄名，與規範 11（避免單字欄名，須加實體前綴）衝突；範例工作表卻是這四個欄名</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沿用範例欄名</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">以範例或條文為準？</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">範例 SYS_PARAM 欄名用 DESCR，縮寫字典是 DESC（DESCRIPTION）；範例的 PARAM 與字典 PARM 亦不一致</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">沿用範例寫法（DESCR）</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">以範例或字典為準？</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">應用帳號 ap_user 對 31 張表都授權 SELECT／INSERT／UPDATE／DELETE；其中 IM_ACCESS_LOG（存取紀錄）、IM_APP_EVENT（狀態事件）、IM_APP_VER（版次快照）性質上只新增不修改，是否收緊為只給 SELECT／INSERT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">四種權限都給</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">依公司慣例是否收緊？</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
 </file>
--- a/docs/db/Table_List_Schema.xlsx
+++ b/docs/db/Table_List_Schema.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">目的：站台名稱、上傳限制、流程政策、存取紀錄排除 IP 等可調參數。來源：本檔預載＋後台維護。主鍵：PARAM_NAME＋PARAM_VALUE。多值參數（如 EXCLUDE_IP）一值一列；ADMIN_EMAIL 由部署時填入，不預載。欄名依規範 11 加 PARAM_ 前綴，與規範範例工作表的 NAME／VALUE／DESCR／MEMO 不同</t>
+          <t xml:space="preserve">目的：站台名稱、上傳限制、流程政策、存取紀錄排除 IP 等可調參數。來源：本檔預載＋後台維護。主鍵：PARAM_NAME＋PARAM_VALUE。多值參數（如 EXCLUDE_IP）一值一列；ADMIN_EMAIL 由部署時填入，不預載。NAME／VALUE／DESC 欄名依規範 11 加 PARAM_ 前綴（NAME 在規範列舉內、DESC 為 Oracle 保留字、VALUE 為 Oracle 關鍵字且與保留字 VALUES 易混淆；與規範範例工作表的 NAME／VALUE／DESCR 不同），MEMO 不是保留字、沿用範例原名</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E90" s="2"/>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E107" s="2"/>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IS_VENDOR_EXEC</t>
+          <t xml:space="preserve">IS_SUP_EXEC</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENDOR_NAME</t>
+          <t xml:space="preserve">SUP_NAME</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       <c r="F144" s="2"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">廠商名稱（本系統無廠商主檔，存文字）</t>
+          <t xml:space="preserve">廠商名稱（自由文字，如「晉泰科技」）。屬規範 12 例外：本系統無廠商主檔，舊系統的廠商只有文字沒有代碼（同一廠商有不同寫法，如「晉泰科技」「晉泰」）；施工廠商是否在公司廠商主檔 CMN_SUP（PX 廠編）內待 DBA 確認</t>
         </is>
       </c>
       <c r="H144" s="2"/>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENDOR_CNTCT</t>
+          <t xml:space="preserve">SUP_CNTCT</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENDOR_TEL</t>
+          <t xml:space="preserve">SUP_TEL</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENDOR_HEAD_CNT</t>
+          <t xml:space="preserve">SUP_HEAD_CNT</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E149" s="2"/>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E166" s="2"/>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E246" s="2"/>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E248" s="2"/>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E261" s="2"/>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">CLOB</t>
         </is>
       </c>
       <c r="E275" s="2"/>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">VARCHAR2(1000 CHAR)</t>
         </is>
       </c>
       <c r="E317" s="2"/>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARAM_MEMO</t>
+          <t xml:space="preserve">MEMO</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">VARCHAR2(1000 CHAR)</t>
         </is>
       </c>
       <c r="E387" s="2"/>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARCHAR2(2000 CHAR)</t>
+          <t xml:space="preserve">VARCHAR2(1000 CHAR)</t>
         </is>
       </c>
       <c r="E402" s="2"/>
